--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-von-se-betroffen.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-von-se-betroffen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-von-se-betroffen.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-von-se-betroffen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-von-se-betroffen.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-von-se-betroffen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-von-se-betroffen.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-von-se-betroffen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-von-se-betroffen.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-ex-von-se-betroffen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
